--- a/data/output/overview.xlsx
+++ b/data/output/overview.xlsx
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Mind the Inconspicuous: Revealing the Hidden Weakness in Aligned LLMs' Refusal Boundaries</t>
+          <t>Malicious LLM-Based Conversational AI Makes Users Reveal Personal Information</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>该论文研究对齐LLM的越狱攻击，通过附加EOS token触发上下文分割现象突破拒绝边界，属于LLM本身的安全性研究。</t>
+          <t>研究恶意LLM对话AI通过系统提示设计主动诱导用户泄露个人信息的攻击手法，属于LLM系统本身被武器化的安全威胁。</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9909,22 +9909,22 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>✅ https://github.com/sherdencooper/XLLM</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2405.20653</t>
+          <t>2506.11680</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - Mind the Inconspicuous Revealing the Hidden Weakness in Aligned LLMs' Refusal Boundaries.pdf</t>
+          <t>papers/USENIX/2025 - Malicious LLM-Based Conversational AI Makes Users Reveal Personal Information.pdf</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/0001LHC00025</t>
+          <t>https://dblp.org/rec/conf/uss/ZhanCSS25</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>PAPILLON: Efficient and Stealthy Fuzz Testing-Powered Jailbreaks for LLMs</t>
+          <t>Mind the Inconspicuous: Revealing the Hidden Weakness in Aligned LLMs' Refusal Boundaries</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -9962,15 +9962,15 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>llm, jailbreak</t>
+          <t>llm</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>本文提出针对LLM的自动化黑盒越狱攻击框架PAPILLON，直接研究LLM本身的安全漏洞（越狱攻击），属于LLM安全核心议题。</t>
+          <t>该论文研究对齐LLM的越狱攻击，通过附加EOS token触发上下文分割现象突破拒绝边界，属于LLM本身的安全性研究。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9990,22 +9990,22 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>✅ https://github.com/aaFrostnova/Papillon</t>
+          <t>✅ https://github.com/sherdencooper/XLLM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2409.14866</t>
+          <t>2405.20653</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - PAPILLON Efficient and Stealthy Fuzz Testing-Powered Jailbreaks for LLMs.pdf</t>
+          <t>papers/USENIX/2025 - Mind the Inconspicuous Revealing the Hidden Weakness in Aligned LLMs' Refusal Boundaries.pdf</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/GongLZRCC0L25</t>
+          <t>https://dblp.org/rec/conf/uss/0001LHC00025</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
+          <t>Mirage in the Eyes: Hallucination Attack on Multi-modal Large Language Models with Only Attention Sink</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10043,15 +10043,15 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>large language model, language model, rag, retrieval-augmented</t>
+          <t>large language model, language model, rag</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>本文提出PoisonedRAG，专门研究RAG系统知识库投毒攻击，属于LLM/RAG系统本身的安全问题（RAG投毒）。</t>
+          <t>该论文针对多模态大语言模型（MLLMs）提出幻觉攻击，利用注意力汇聚行为生成对抗性视觉输入触发幻觉内容，属于对LLM系统本身的安全攻击研究。</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -10071,22 +10071,22 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>✅ https://github.com/sleeepeer/PoisonedRAG</t>
+          <t>✅ https://huggingface.co/RachelHGF/Mirage-in-the-Eyes</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2402.07867</t>
+          <t>2501.15269</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - PoisonedRAG Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Langua.pdf</t>
+          <t>papers/USENIX/2025 - Mirage in the Eyes Hallucination Attack on Multi-modal Large Language Models with Only Att.pdf</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/ZouGW025</t>
+          <t>https://dblp.org/rec/conf/uss/Wang0SW00TD025</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>PrivacyXray: Detecting Privacy Breaches in LLMs through Semantic Consistency and Probability Certainty</t>
+          <t>PAPILLON: Efficient and Stealthy Fuzz Testing-Powered Jailbreaks for LLMs</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -10124,15 +10124,15 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>llm</t>
+          <t>llm, jailbreak</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>该论文直接研究LLM推理过程中的隐私泄露检测问题，针对针对LLM的隐私提取攻击（如越狱）提出防御框架，属于LLM本身安全性研究。</t>
+          <t>本文提出针对LLM的自动化黑盒越狱攻击框架PAPILLON，直接研究LLM本身的安全漏洞（越狱攻击），属于LLM安全核心议题。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10152,22 +10152,22 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>✅ https://github.com/aaFrostnova/Papillon</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2506.19563</t>
+          <t>2409.14866</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - PrivacyXray Detecting Privacy Breaches in LLMs through Semantic Consistency and Probabilit.pdf</t>
+          <t>papers/USENIX/2025 - PAPILLON Efficient and Stealthy Fuzz Testing-Powered Jailbreaks for LLMs.pdf</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/HeLL0025</t>
+          <t>https://dblp.org/rec/conf/uss/GongLZRCC0L25</t>
         </is>
       </c>
     </row>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10205,15 +10205,15 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>large language model, language model</t>
+          <t>large language model, language model, rag, retrieval-augmented</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
-          <t>研究通过优化提示从LLM中提取个人身份信息（PII），属于针对LLM系统本身的隐私攻击/数据提取攻击。</t>
+          <t>本文提出PoisonedRAG，专门研究RAG系统知识库投毒攻击，属于LLM/RAG系统本身的安全问题（RAG投毒）。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -10233,18 +10233,22 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>✅ https://doi.org/10.5281/zenodo.15638376</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>✅ https://github.com/sleeepeer/PoisonedRAG</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2402.07867</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - Private Investigator Extracting Personally Identifiable Information from Large Language Mo.pdf</t>
+          <t>papers/USENIX/2025 - PoisonedRAG Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Langua.pdf</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/KeumSM0S25</t>
+          <t>https://dblp.org/rec/conf/uss/ZouGW025</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10263,7 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Prompt Obfuscation for Large Language Models</t>
+          <t>PrivacyXray: Detecting Privacy Breaches in LLMs through Semantic Consistency and Probability Certainty</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10282,15 +10286,15 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>large language model, language model</t>
+          <t>llm</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>该论文研究保护LLM系统提示（system prompt）知识产权免遭提取攻击的防御机制（提示混淆），属于LLM系统本身的安全防护问题。</t>
+          <t>该论文直接研究LLM推理过程中的隐私泄露检测问题，针对针对LLM的隐私提取攻击（如越狱）提出防御框架，属于LLM本身安全性研究。</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -10310,22 +10314,22 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2409.11026</t>
+          <t>2506.19563</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - Prompt Obfuscation for Large Language Models.pdf</t>
+          <t>papers/USENIX/2025 - PrivacyXray Detecting Privacy Breaches in LLMs through Semantic Consistency and Probabilit.pdf</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/PapeMES25</t>
+          <t>https://dblp.org/rec/conf/uss/HeLL0025</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10344,7 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Refusal Is Not an Option: Unlearning Safety Alignment of Large Language Models</t>
+          <t>Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10367,11 +10371,11 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
-          <t>该论文研究对LLM安全对齐（safety alignment）的反学习（unlearning）攻击，属于针对LLM本身安全机制的攻击研究。</t>
+          <t>研究通过优化提示从LLM中提取个人身份信息（PII），属于针对LLM系统本身的隐私攻击/数据提取攻击。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10391,18 +10395,18 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>✅ https://doi.org/10.5281/zenodo.15628860</t>
+          <t>✅ https://doi.org/10.5281/zenodo.15638376</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - Refusal Is Not an Option Unlearning Safety Alignment of Large Language Models.pdf</t>
+          <t>papers/USENIX/2025 - Private Investigator Extracting Personally Identifiable Information from Large Language Mo.pdf</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/SongKK0S25</t>
+          <t>https://dblp.org/rec/conf/uss/KeumSM0S25</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10421,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>SelfDefend: LLMs Can Defend Themselves against Jailbreaking in a Practical Manner</t>
+          <t>Prompt Obfuscation for Large Language Models</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10440,15 +10444,15 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>llm, jailbreak, jailbreaking</t>
+          <t>large language model, language model</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>本文直接研究LLM自身的越狱攻击防御机制，属于LLM安全核心问题。</t>
+          <t>该论文研究保护LLM系统提示（system prompt）知识产权免遭提取攻击的防御机制（提示混淆），属于LLM系统本身的安全防护问题。</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10473,17 +10477,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2406.05498</t>
+          <t>2409.11026</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - SelfDefend LLMs Can Defend Themselves against Jailbreaking in a Practical Manner.pdf</t>
+          <t>papers/USENIX/2025 - Prompt Obfuscation for Large Language Models.pdf</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/WangWJL00L0LR25</t>
+          <t>https://dblp.org/rec/conf/uss/PapeMES25</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10502,7 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>StruQ: Defending Against Prompt Injection with Structured Queries</t>
+          <t>Refusal Is Not an Option: Unlearning Safety Alignment of Large Language Models</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10506,7 +10510,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -10521,15 +10525,15 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>prompt injection</t>
+          <t>large language model, language model</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
-          <t>本文专门研究针对LLM的提示注入攻击防御，通过结构化查询将提示与数据分离，属于LLM系统安全研究。</t>
+          <t>该论文研究对LLM安全对齐（safety alignment）的反学习（unlearning）攻击，属于针对LLM本身安全机制的攻击研究。</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10549,22 +10553,18 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>✅ https://github.com/Sizhe-Chen/StruQ</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2402.06363</t>
-        </is>
-      </c>
+          <t>✅ https://doi.org/10.5281/zenodo.15628860</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - StruQ Defending Against Prompt Injection with Structured Queries.pdf</t>
+          <t>papers/USENIX/2025 - Refusal Is Not an Option Unlearning Safety Alignment of Large Language Models.pdf</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/ChenPS025</t>
+          <t>https://dblp.org/rec/conf/uss/SongKK0S25</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Topic-FlipRAG: Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augmented Generation Models</t>
+          <t>SelfDefend: LLMs Can Defend Themselves against Jailbreaking in a Practical Manner</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -10602,15 +10602,15 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>rag, retrieval-augmented</t>
+          <t>llm, jailbreak, jailbreaking</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>该论文研究针对RAG系统的对抗性知识投毒攻击，属于LLM/RAG系统本身的安全问题（RAG投毒），符合agent/LLM安全范畴。</t>
+          <t>本文直接研究LLM自身的越狱攻击防御机制，属于LLM安全核心问题。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10630,22 +10630,22 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>✅ https://github.com/LauJames/Topic-FlipRAG</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2502.01386</t>
+          <t>2406.05498</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - Topic-FlipRAG Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augme.pdf</t>
+          <t>papers/USENIX/2025 - SelfDefend LLMs Can Defend Themselves against Jailbreaking in a Practical Manner.pdf</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/GongC0CY00L25</t>
+          <t>https://dblp.org/rec/conf/uss/WangWJL00L0LR25</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
+          <t>StruQ: Defending Against Prompt Injection with Structured Queries</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>framework/system</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -10683,15 +10683,15 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>llm</t>
+          <t>prompt injection</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.72</v>
+        <v>0.97</v>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
-          <t>该论文提出的上下文溯源框架明确应用于RAG/agent系统中提示注入、知识投毒等攻击的事后取证分析，属于LLM/agent安全防御支撑工具。</t>
+          <t>本文专门研究针对LLM的提示注入攻击防御，通过结构化查询将提示与数据分离，属于LLM系统安全研究。</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10711,22 +10711,22 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>✅ https://github.com/Wang-Yanting/TracLLM</t>
+          <t>✅ https://github.com/Sizhe-Chen/StruQ</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2506.04202</t>
+          <t>2402.06363</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - TracLLM A Generic Framework for Attributing Long Context LLMs.pdf</t>
+          <t>papers/USENIX/2025 - StruQ Defending Against Prompt Injection with Structured Queries.pdf</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/WangZG025</t>
+          <t>https://dblp.org/rec/conf/uss/ChenPS025</t>
         </is>
       </c>
     </row>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>TwinBreak: Jailbreaking LLM Security Alignments based on Twin Prompts</t>
+          <t>Topic-FlipRAG: Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augmented Generation Models</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -10764,15 +10764,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>llm, jailbreak, jailbreaking</t>
+          <t>rag, retrieval-augmented</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>该论文直接研究LLM安全对齐机制的越狱攻击（jailbreak），通过剪枝安全参数绕过LLM的安全机制，属于LLM本身安全性的核心研究。</t>
+          <t>该论文研究针对RAG系统的对抗性知识投毒攻击，属于LLM/RAG系统本身的安全问题（RAG投毒），符合agent/LLM安全范畴。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -10792,22 +10792,22 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>✅ https://github.com/LauJames/Topic-FlipRAG</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2506.07596</t>
+          <t>2502.01386</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - TwinBreak Jailbreaking LLM Security Alignments based on Twin Prompts.pdf</t>
+          <t>papers/USENIX/2025 - Topic-FlipRAG Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augme.pdf</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/KraussDD25</t>
+          <t>https://dblp.org/rec/conf/uss/GongC0CY00L25</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Unsafe LLM-Based Search: Quantitative Analysis and Mitigation of Safety Risks in AI Web Search</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>benchmark/measurement</t>
+          <t>framework/system</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -10849,11 +10849,11 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
-          <t>论文研究AI驱动搜索引擎（基于LLM）在引用恶意内容/URL方面的安全风险，属于LLM/agent系统本身的安全问题（RAG投毒/恶意内容引用），并提出基于agent的防御方案。</t>
+          <t>该论文提出的上下文溯源框架明确应用于RAG/agent系统中提示注入、知识投毒等攻击的事后取证分析，属于LLM/agent安全防御支撑工具。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -10873,22 +10873,22 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>✅ https://github.com/Wang-Yanting/TracLLM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2502.04951</t>
+          <t>2506.04202</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - Unsafe LLM-Based Search Quantitative Analysis and Mitigation of Safety Risks in AI Web Sea.pdf</t>
+          <t>papers/USENIX/2025 - TracLLM A Generic Framework for Attributing Long Context LLMs.pdf</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/LuoPL0LZ025</t>
+          <t>https://dblp.org/rec/conf/uss/WangZG025</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs</t>
+          <t>TwinBreak: Jailbreaking LLM Security Alignments based on Twin Prompts</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>benchmark/measurement</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -10926,15 +10926,15 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>llm</t>
+          <t>llm, jailbreak, jailbreaking</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>研究代码生成LLM产生幻觉包名所导致的软件供应链安全威胁，属于LLM本身的安全问题（LLM供应链后门/幻觉攻击），而非仅用LLM做传统安全任务。</t>
+          <t>该论文直接研究LLM安全对齐机制的越狱攻击（jailbreak），通过剪枝安全参数绕过LLM的安全机制，属于LLM本身安全性的核心研究。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -10954,22 +10954,22 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>✅ https://github.com/Spracks/PackageHallucinations</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2406.10279</t>
+          <t>2506.07596</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Gene.pdf</t>
+          <t>papers/USENIX/2025 - TwinBreak Jailbreaking LLM Security Alignments based on Twin Prompts.pdf</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/SpracklenWSMV25</t>
+          <t>https://dblp.org/rec/conf/uss/KraussDD25</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>When LLMs Go Online: The Emerging Threat of Web-Enabled LLMs</t>
+          <t>Unsafe LLM-Based Search: Quantitative Analysis and Mitigation of Safety Risks in AI Web Search</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>benchmark/measurement</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
-          <t>研究网页工具增强的LLM智能体被滥用于网络攻击（PII收集、钓鱼邮件等）的安全威胁，属于LLM agent自身的安全问题。</t>
+          <t>论文研究AI驱动搜索引擎（基于LLM）在引用恶意内容/URL方面的安全风险，属于LLM/agent系统本身的安全问题（RAG投毒/恶意内容引用），并提出基于agent的防御方案。</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -11035,22 +11035,22 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>✅ https://zenodo.org/doi/10.5281/zenodo.13691327</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2410.14569</t>
+          <t>2502.04951</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>papers/USENIX/2025 - When LLMs Go Online The Emerging Threat of Web-Enabled LLMs.pdf</t>
+          <t>papers/USENIX/2025 - Unsafe LLM-Based Search Quantitative Analysis and Mitigation of Safety Risks in AI Web Sea.pdf</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/KimSN0L25</t>
+          <t>https://dblp.org/rec/conf/uss/LuoPL0LZ025</t>
         </is>
       </c>
     </row>
@@ -11058,14 +11058,14 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Malicious LLM-Based Conversational AI Makes Users Reveal Personal Information</t>
+          <t>We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>benchmark/measurement</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11096,17 +11096,17 @@
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>研究恶意LLM对话AI通过系统提示设计主动诱导用户泄露个人信息的攻击手法，属于LLM系统本身被武器化的安全威胁。</t>
+          <t>研究代码生成LLM产生幻觉包名所导致的软件供应链安全威胁，属于LLM本身的安全问题（LLM供应链后门/幻觉攻击），而非仅用LLM做传统安全任务。</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -11116,18 +11116,22 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>✅ https://github.com/Spracks/PackageHallucinations</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2506.11680</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>2406.10279</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>papers/USENIX/2025 - We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Gene.pdf</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/ZhanCSS25</t>
+          <t>https://dblp.org/rec/conf/uss/SpracklenWSMV25</t>
         </is>
       </c>
     </row>
@@ -11135,14 +11139,14 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Mirage in the Eyes: Hallucination Attack on Multi-modal Large Language Models with Only Attention Sink</t>
+          <t>When LLMs Go Online: The Emerging Threat of Web-Enabled LLMs</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -11165,7 +11169,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>large language model, language model, rag</t>
+          <t>llm</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -11173,17 +11177,17 @@
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
-          <t>该论文针对多模态大语言模型（MLLMs）提出幻觉攻击，利用注意力汇聚行为生成对抗性视觉输入触发幻觉内容，属于对LLM系统本身的安全攻击研究。</t>
+          <t>研究网页工具增强的LLM智能体被滥用于网络攻击（PII收集、钓鱼邮件等）的安全威胁，属于LLM agent自身的安全问题。</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -11193,18 +11197,22 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>✅ https://huggingface.co/RachelHGF/Mirage-in-the-Eyes</t>
+          <t>✅ https://zenodo.org/doi/10.5281/zenodo.13691327</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2501.15269</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>2410.14569</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>papers/USENIX/2025 - When LLMs Go Online The Emerging Threat of Web-Enabled LLMs.pdf</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/uss/Wang0SW00TD025</t>
+          <t>https://dblp.org/rec/conf/uss/KimSN0L25</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13703,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks</t>
+          <t>BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -13718,15 +13726,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>prompt injection</t>
+          <t>large language model, language model</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="J3" s="15" t="inlineStr">
         <is>
-          <t>本文专门研究LLM集成应用与智能体中的提示注入攻击检测，属于LLM/agent本身安全防御研究。</t>
+          <t>该论文专门研究LLM后门攻击的检测防御技术（后门扫描），属于LLM本身的安全问题，符合LLM供应链后门/安全防御范畴。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -13746,22 +13754,18 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>✅ https://github.com/liu00222/Open-Prompt-Injection</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2504.11358</t>
-        </is>
-      </c>
+          <t>✅ https://github.com/SolidShen/BAIT</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>papers/SP/2025 - DataSentinel A Game-Theoretic Detection of Prompt Injection Attacks.pdf</t>
+          <t>papers/SP/2025 - BAIT Large Language Model Backdoor Scanning by Inverting Attack Target.pdf</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/LiuJ0SG25</t>
+          <t>https://dblp.org/rec/conf/sp/Shen0000GY0AM025</t>
         </is>
       </c>
     </row>
@@ -13776,7 +13780,7 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Fun-tuning: Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prompt Injection Attacks via the Fine-Tuning Interface</t>
+          <t>DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -13784,7 +13788,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -13799,15 +13803,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>llm, prompt injection</t>
+          <t>prompt injection</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>该论文研究针对闭源LLM的优化型提示注入攻击，利用微调接口泄露的损失信息构造对抗性提示，属于LLM本身的安全攻击研究。</t>
+          <t>本文专门研究LLM集成应用与智能体中的提示注入攻击检测，属于LLM/agent本身安全防御研究。</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -13827,22 +13831,22 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>✅ https://github.com/earlence-security/fun-tuning</t>
+          <t>✅ https://github.com/liu00222/Open-Prompt-Injection</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2501.09798</t>
+          <t>2504.11358</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>papers/SP/2025 - Fun-tuning Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prom.pdf</t>
+          <t>papers/SP/2025 - DataSentinel A Game-Theoretic Detection of Prompt Injection Attacks.pdf</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/LabunetsPHFF25</t>
+          <t>https://dblp.org/rec/conf/sp/LiuJ0SG25</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13861,7 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Prompt Inversion Attack Against Collaborative Inference of Large Language Models</t>
+          <t>Fun-tuning: Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prompt Injection Attacks via the Fine-Tuning Interface</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -13880,15 +13884,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>large language model, language model</t>
+          <t>llm, prompt injection</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="J5" s="15" t="inlineStr">
         <is>
-          <t>本文研究LLM协作推理场景下的提示反演攻击，直接针对LLM系统本身的隐私安全威胁，属于LLM系统安全研究。</t>
+          <t>该论文研究针对闭源LLM的优化型提示注入攻击，利用微调接口泄露的损失信息构造对抗性提示，属于LLM本身的安全攻击研究。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -13908,22 +13912,22 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>✅ https://github.com/earlence-security/fun-tuning</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2503.09022</t>
+          <t>2501.09798</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>papers/SP/2025 - Prompt Inversion Attack Against Collaborative Inference of Large Language Models.pdf</t>
+          <t>papers/SP/2025 - Fun-tuning Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prom.pdf</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/0004ZWXYLZ25</t>
+          <t>https://dblp.org/rec/conf/sp/LabunetsPHFF25</t>
         </is>
       </c>
     </row>
@@ -13931,14 +13935,14 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target</t>
+          <t>Fuzz-Testing Meets LLM-Based Agents: An Automated and Efficient Framework for Jailbreaking Text-to-Image Generation Models</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -13946,7 +13950,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13961,25 +13965,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>large language model, language model</t>
+          <t>agent, llm, jailbreak, jailbreaking</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>该论文专门研究LLM后门攻击的检测防御技术（后门扫描），属于LLM本身的安全问题，符合LLM供应链后门/安全防御范畴。</t>
+          <t>本文研究利用LLM智能体驱动的模糊测试框架对文本生成图像模型实施越狱攻击，属于针对AI系统安全性（越狱攻击）的研究，LLM agent是攻击框架的核心组件。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -13989,14 +13993,22 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+          <t>✅ https://github.com/YingkaiD/JailFuzzer</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2408.00523</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>papers/SP/2025 - Fuzz-Testing Meets LLM-Based Agents An Automated and Efficient Framework for Jailbreaking.pdf</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/Shen0000GY0AM025</t>
+          <t>https://dblp.org/rec/conf/sp/DongM00G25</t>
         </is>
       </c>
     </row>
@@ -14004,14 +14016,14 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Codebreaker: Dynamic Extraction Attacks on Code Language Models</t>
+          <t>GPTracker: A Large-Scale Measurement of Misused GPTs</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -14019,7 +14031,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>benchmark/measurement</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -14034,25 +14046,25 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>language model</t>
+          <t>gpt</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
-          <t>本文研究针对LLM代码助手（CodeLLMs）的训练数据提取攻击，属于LLM模型本身的隐私安全问题（训练数据泄露/记忆攻击），而非仅将LLM用作传统安全工具。</t>
+          <t>本文对OpenAI GPT Store中LLM驱动的智能体（GPTs）的滥用行为进行大规模测量研究，直接针对AI agent系统的安全问题（如绕过审核、恶意API集成、钓鱼域名等），属于LLM/agent本身的安全研究。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -14062,14 +14074,18 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>✅ https://github.com/TrustAIRLab/GPTracker</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>papers/SP/2025 - GPTracker A Large-Scale Measurement of Misused GPTs.pdf</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/HanDM00ZW025</t>
+          <t>https://dblp.org/rec/conf/sp/0001S0Z25</t>
         </is>
       </c>
     </row>
@@ -14077,14 +14093,14 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Fuzz-Testing Meets LLM-Based Agents: An Automated and Efficient Framework for Jailbreaking Text-to-Image Generation Models</t>
+          <t>Make a Feint to the East While Attacking in the West: Blinding LLM-Based Code Auditors with Flashboom Attacks</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -14107,25 +14123,25 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>agent, llm, jailbreak, jailbreaking</t>
+          <t>llm</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>本文研究利用LLM智能体驱动的模糊测试框架对文本生成图像模型实施越狱攻击，属于针对AI系统安全性（越狱攻击）的研究，LLM agent是攻击框架的核心组件。</t>
+          <t>本文研究针对基于LLM的代码审计系统的对抗性攻击（注意力转移攻击），属于攻击LLM系统本身安全性的研究，而非仅将LLM用作传统安全工具。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -14135,18 +14151,18 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>✅ https://github.com/YingkaiD/JailFuzzer</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2408.00523</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>✅ https://github.com/oxygen-hunter/Flashboom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>papers/SP/2025 - Make a Feint to the East While Attacking in the West Blinding LLM-Based Code Auditors with.pdf</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/DongM00G25</t>
+          <t>https://dblp.org/rec/conf/sp/LiLWZX00X25</t>
         </is>
       </c>
     </row>
@@ -14154,14 +14170,14 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>GPTracker: A Large-Scale Measurement of Misused GPTs</t>
+          <t>Modifier Unlocked: Jailbreaking Text-to-Image Models Through Prompts</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -14169,7 +14185,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>benchmark/measurement</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -14184,25 +14200,25 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>jailbreak, jailbreaking</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>本文对OpenAI GPT Store中LLM驱动的智能体（GPTs）的滥用行为进行大规模测量研究，直接针对AI agent系统的安全问题（如绕过审核、恶意API集成、钓鱼域名等），属于LLM/agent本身的安全研究。</t>
+          <t>本文研究对文本到图像生成模型的越狱攻击（jailbreak），属于针对AI生成模型本身的安全性研究，符合LLM/生成模型越狱攻击范畴。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -14212,14 +14228,18 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>✅ https://github.com/TrustAIRLab/GPTracker</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>papers/SP/2025 - Modifier Unlocked Jailbreaking Text-to-Image Models Through Prompts.pdf</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/0001S0Z25</t>
+          <t>https://dblp.org/rec/conf/sp/LiuM0B25</t>
         </is>
       </c>
     </row>
@@ -14227,14 +14247,14 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Make a Feint to the East While Attacking in the West: Blinding LLM-Based Code Auditors with Flashboom Attacks</t>
+          <t>On the (In)Security of LLM App Stores</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -14242,7 +14262,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>benchmark/measurement</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -14261,21 +14281,21 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>本文研究针对基于LLM的代码审计系统的对抗性攻击（注意力转移攻击），属于攻击LLM系统本身安全性的研究，而非仅将LLM用作传统安全工具。</t>
+          <t>本文系统研究LLM应用商店（GPT Store等）中自定义LLM应用的安全风险，包括恶意意图、后门、有害内容生成等，属于LLM/agent系统本身的安全研究。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -14285,14 +14305,22 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>✅ https://github.com/oxygen-hunter/Flashboom</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2407.08422</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>papers/SP/2025 - On the (In)Security of LLM App Stores.pdf</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/LiLWZX00X25</t>
+          <t>https://dblp.org/rec/conf/sp/HouZW25</t>
         </is>
       </c>
     </row>
@@ -14300,14 +14328,14 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>📃 相关·仅摘要(付费墙未下载)</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>✅ 相关·已下载全文</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Modifier Unlocked: Jailbreaking Text-to-Image Models Through Prompts</t>
+          <t>Prompt Inversion Attack Against Collaborative Inference of Large Language Models</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -14330,7 +14358,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>jailbreak, jailbreaking</t>
+          <t>large language model, language model</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -14338,17 +14366,17 @@
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
-          <t>本文研究对文本到图像生成模型的越狱攻击（jailbreak），属于针对AI生成模型本身的安全性研究，符合LLM/生成模型越狱攻击范畴。</t>
+          <t>本文研究LLM协作推理场景下的提示反演攻击，直接针对LLM系统本身的隐私安全威胁，属于LLM系统安全研究。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>仅摘要</t>
+          <t>全文</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -14361,11 +14389,19 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2503.09022</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>papers/SP/2025 - Prompt Inversion Attack Against Collaborative Inference of Large Language Models.pdf</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/LiuM0B25</t>
+          <t>https://dblp.org/rec/conf/sp/0004ZWXYLZ25</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14416,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>On the (In)Security of LLM App Stores</t>
+          <t>Codebreaker: Dynamic Extraction Attacks on Code Language Models</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -14388,7 +14424,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>benchmark/measurement</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -14403,15 +14439,15 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>llm</t>
+          <t>language model</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>本文系统研究LLM应用商店（GPT Store等）中自定义LLM应用的安全风险，包括恶意意图、后门、有害内容生成等，属于LLM/agent系统本身的安全研究。</t>
+          <t>本文研究针对LLM代码助手（CodeLLMs）的训练数据提取攻击，属于LLM模型本身的隐私安全问题（训练数据泄露/记忆攻击），而非仅将LLM用作传统安全工具。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14434,15 +14470,11 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2407.08422</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://dblp.org/rec/conf/sp/HouZW25</t>
+          <t>https://dblp.org/rec/conf/sp/HanDM00ZW025</t>
         </is>
       </c>
     </row>
